--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.2379888402214</v>
+        <v>11.41367318653598</v>
       </c>
       <c r="D2" t="n">
-        <v>34.09464484719317</v>
+        <v>5.54037978766889</v>
       </c>
       <c r="E2" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F2" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.6008363314632</v>
+        <v>12.77263590386277</v>
       </c>
       <c r="D3" t="n">
-        <v>57.58067043688969</v>
+        <v>9.356858945994574</v>
       </c>
       <c r="E3" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F3" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>74.07646893461423</v>
+        <v>12.03742620187481</v>
       </c>
       <c r="D4" t="n">
-        <v>1.033311366042988</v>
+        <v>0.1679130969819856</v>
       </c>
       <c r="E4" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F4" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.89848599151711</v>
+        <v>10.22100397362153</v>
       </c>
       <c r="D5" t="n">
-        <v>63.3981436262041</v>
+        <v>10.30219833925817</v>
       </c>
       <c r="E5" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F5" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.92056306414517</v>
+        <v>6.162091497923591</v>
       </c>
       <c r="D6" t="n">
-        <v>38.49615285639343</v>
+        <v>6.255624839163932</v>
       </c>
       <c r="E6" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F6" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.1241366439354</v>
+        <v>4.570172204639503</v>
       </c>
       <c r="D7" t="n">
-        <v>29.83817882429449</v>
+        <v>4.848704058947855</v>
       </c>
       <c r="E7" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F7" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.8742249211338</v>
+        <v>5.829561549684243</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88349778098137</v>
+        <v>5.831068389409472</v>
       </c>
       <c r="E8" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F8" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.17492527776552</v>
+        <v>8.478425357636898</v>
       </c>
       <c r="D9" t="n">
-        <v>50.43796748464769</v>
+        <v>8.19616971625525</v>
       </c>
       <c r="E9" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F9" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.4341994777031</v>
+        <v>6.245557415126754</v>
       </c>
       <c r="D10" t="n">
-        <v>36.59378400966594</v>
+        <v>5.946489901570716</v>
       </c>
       <c r="E10" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F10" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>73.36650405942966</v>
+        <v>11.92205690965732</v>
       </c>
       <c r="D11" t="n">
-        <v>71.60883859005448</v>
+        <v>11.63643627088385</v>
       </c>
       <c r="E11" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F11" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>71.65462659917227</v>
+        <v>11.6438768223655</v>
       </c>
       <c r="D12" t="n">
-        <v>70.33066417700049</v>
+        <v>11.42873292876258</v>
       </c>
       <c r="E12" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F12" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>64.57838837004779</v>
+        <v>10.49398811013277</v>
       </c>
       <c r="D13" t="n">
-        <v>62.64860118138586</v>
+        <v>10.1803976919752</v>
       </c>
       <c r="E13" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F13" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>90.57133413177893</v>
+        <v>14.71784179641408</v>
       </c>
       <c r="D14" t="n">
-        <v>88.6934106280127</v>
+        <v>14.41267922705206</v>
       </c>
       <c r="E14" t="n">
-        <v>18.68604620551828</v>
+        <v>3.036482508396721</v>
       </c>
       <c r="F14" t="n">
-        <v>22.07753473627957</v>
+        <v>3.587599394645431</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
